--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="140">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -433,6 +433,12 @@
   </si>
   <si>
     <t>1405/06/20</t>
+  </si>
+  <si>
+    <t>1405/06/23</t>
+  </si>
+  <si>
+    <t>سیگلر قهوه</t>
   </si>
 </sst>
 </file>
@@ -942,7 +948,7 @@
       </c>
       <c r="H2" s="8">
         <f>C115</f>
-        <v>4490000</v>
+        <v>4790000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2372,17 +2378,23 @@
     <row r="103" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="7">
         <f t="shared" si="4"/>
-        <v>4490000</v>
-      </c>
-      <c r="B103" s="7"/>
+        <v>4790000</v>
+      </c>
+      <c r="B103" s="7">
+        <v>300000</v>
+      </c>
       <c r="C103" s="7"/>
-      <c r="D103" s="1"/>
-      <c r="E103" s="1"/>
+      <c r="D103" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="104" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="7">
         <f t="shared" si="4"/>
-        <v>4490000</v>
+        <v>4790000</v>
       </c>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -2392,7 +2404,7 @@
     <row r="105" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="7">
         <f t="shared" si="4"/>
-        <v>4490000</v>
+        <v>4790000</v>
       </c>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -2402,7 +2414,7 @@
     <row r="106" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
         <f t="shared" si="4"/>
-        <v>4490000</v>
+        <v>4790000</v>
       </c>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -2412,7 +2424,7 @@
     <row r="107" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <f t="shared" si="4"/>
-        <v>4490000</v>
+        <v>4790000</v>
       </c>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -2422,7 +2434,7 @@
     <row r="108" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <f t="shared" si="4"/>
-        <v>4490000</v>
+        <v>4790000</v>
       </c>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -2432,7 +2444,7 @@
     <row r="109" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <f t="shared" si="4"/>
-        <v>4490000</v>
+        <v>4790000</v>
       </c>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -2442,7 +2454,7 @@
     <row r="110" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <f t="shared" si="4"/>
-        <v>4490000</v>
+        <v>4790000</v>
       </c>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -2452,7 +2464,7 @@
     <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <f t="shared" si="4"/>
-        <v>4490000</v>
+        <v>4790000</v>
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -2462,7 +2474,7 @@
     <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <f xml:space="preserve"> A111 +B112-C112</f>
-        <v>4490000</v>
+        <v>4790000</v>
       </c>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2472,7 +2484,7 @@
     <row r="113" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="8">
         <f>SUM(B93:B112)+B87</f>
-        <v>17575000</v>
+        <v>17875000</v>
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
@@ -2483,7 +2495,7 @@
     <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
-        <v>4490000</v>
+        <v>4790000</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="141">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -439,6 +439,9 @@
   </si>
   <si>
     <t>سیگلر قهوه</t>
+  </si>
+  <si>
+    <t>1405/07/01</t>
   </si>
 </sst>
 </file>
@@ -948,7 +951,7 @@
       </c>
       <c r="H2" s="8">
         <f>C115</f>
-        <v>4790000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2394,17 +2397,23 @@
     <row r="104" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="7">
         <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="B104" s="7"/>
+      <c r="C104" s="7">
         <v>4790000</v>
       </c>
-      <c r="B104" s="7"/>
-      <c r="C104" s="7"/>
-      <c r="D104" s="1"/>
-      <c r="E104" s="1"/>
+      <c r="D104" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="105" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="7">
         <f t="shared" si="4"/>
-        <v>4790000</v>
+        <v>0</v>
       </c>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -2414,7 +2423,7 @@
     <row r="106" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
         <f t="shared" si="4"/>
-        <v>4790000</v>
+        <v>0</v>
       </c>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -2424,7 +2433,7 @@
     <row r="107" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <f t="shared" si="4"/>
-        <v>4790000</v>
+        <v>0</v>
       </c>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -2434,7 +2443,7 @@
     <row r="108" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <f t="shared" si="4"/>
-        <v>4790000</v>
+        <v>0</v>
       </c>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -2444,7 +2453,7 @@
     <row r="109" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <f t="shared" si="4"/>
-        <v>4790000</v>
+        <v>0</v>
       </c>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -2454,7 +2463,7 @@
     <row r="110" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <f t="shared" si="4"/>
-        <v>4790000</v>
+        <v>0</v>
       </c>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -2464,7 +2473,7 @@
     <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <f t="shared" si="4"/>
-        <v>4790000</v>
+        <v>0</v>
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -2474,7 +2483,7 @@
     <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <f xml:space="preserve"> A111 +B112-C112</f>
-        <v>4790000</v>
+        <v>0</v>
       </c>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2488,14 +2497,14 @@
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
-        <v>12752000</v>
+        <v>17542000</v>
       </c>
     </row>
     <row r="114" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
-        <v>4790000</v>
+        <v>0</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="142">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -442,6 +442,9 @@
   </si>
   <si>
     <t>1405/07/01</t>
+  </si>
+  <si>
+    <t>1405/07/09</t>
   </si>
 </sst>
 </file>
@@ -951,7 +954,7 @@
       </c>
       <c r="H2" s="8">
         <f>C115</f>
-        <v>0</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2413,17 +2416,23 @@
     <row r="105" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="B105" s="7"/>
+        <v>230000</v>
+      </c>
+      <c r="B105" s="7">
+        <v>230000</v>
+      </c>
       <c r="C105" s="7"/>
-      <c r="D105" s="1"/>
-      <c r="E105" s="1"/>
+      <c r="D105" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="106" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -2433,7 +2442,7 @@
     <row r="107" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -2443,7 +2452,7 @@
     <row r="108" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -2453,7 +2462,7 @@
     <row r="109" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -2463,7 +2472,7 @@
     <row r="110" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -2473,7 +2482,7 @@
     <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -2483,7 +2492,7 @@
     <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <f xml:space="preserve"> A111 +B112-C112</f>
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2493,7 +2502,7 @@
     <row r="113" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="8">
         <f>SUM(B93:B112)+B87</f>
-        <v>17875000</v>
+        <v>18105000</v>
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
@@ -2504,7 +2513,7 @@
     <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="164011"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="144">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -445,6 +445,12 @@
   </si>
   <si>
     <t>1405/07/09</t>
+  </si>
+  <si>
+    <t>1405/07/10</t>
+  </si>
+  <si>
+    <t>قهوه بستنی</t>
   </si>
 </sst>
 </file>
@@ -954,7 +960,7 @@
       </c>
       <c r="H2" s="8">
         <f>C115</f>
-        <v>230000</v>
+        <v>580000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2432,17 +2438,23 @@
     <row r="106" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
         <f t="shared" si="4"/>
-        <v>230000</v>
-      </c>
-      <c r="B106" s="7"/>
+        <v>580000</v>
+      </c>
+      <c r="B106" s="7">
+        <v>350000</v>
+      </c>
       <c r="C106" s="7"/>
-      <c r="D106" s="1"/>
-      <c r="E106" s="1"/>
+      <c r="D106" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="107" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <f t="shared" si="4"/>
-        <v>230000</v>
+        <v>580000</v>
       </c>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -2452,7 +2464,7 @@
     <row r="108" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <f t="shared" si="4"/>
-        <v>230000</v>
+        <v>580000</v>
       </c>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -2462,7 +2474,7 @@
     <row r="109" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <f t="shared" si="4"/>
-        <v>230000</v>
+        <v>580000</v>
       </c>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -2472,7 +2484,7 @@
     <row r="110" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <f t="shared" si="4"/>
-        <v>230000</v>
+        <v>580000</v>
       </c>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -2482,7 +2494,7 @@
     <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <f t="shared" si="4"/>
-        <v>230000</v>
+        <v>580000</v>
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -2492,7 +2504,7 @@
     <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <f xml:space="preserve"> A111 +B112-C112</f>
-        <v>230000</v>
+        <v>580000</v>
       </c>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2502,7 +2514,7 @@
     <row r="113" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="8">
         <f>SUM(B93:B112)+B87</f>
-        <v>18105000</v>
+        <v>18455000</v>
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
@@ -2513,7 +2525,7 @@
     <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
-        <v>230000</v>
+        <v>580000</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="146">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -451,6 +451,12 @@
   </si>
   <si>
     <t>قهوه بستنی</t>
+  </si>
+  <si>
+    <t>1405/07/12</t>
+  </si>
+  <si>
+    <t>سیگار تخمه ژاپنی</t>
   </si>
 </sst>
 </file>
@@ -960,7 +966,7 @@
       </c>
       <c r="H2" s="8">
         <f>C115</f>
-        <v>580000</v>
+        <v>952000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2454,17 +2460,23 @@
     <row r="107" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <f t="shared" si="4"/>
-        <v>580000</v>
-      </c>
-      <c r="B107" s="7"/>
+        <v>952000</v>
+      </c>
+      <c r="B107" s="7">
+        <v>372000</v>
+      </c>
       <c r="C107" s="7"/>
-      <c r="D107" s="1"/>
-      <c r="E107" s="1"/>
+      <c r="D107" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="108" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <f t="shared" si="4"/>
-        <v>580000</v>
+        <v>952000</v>
       </c>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -2474,7 +2486,7 @@
     <row r="109" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <f t="shared" si="4"/>
-        <v>580000</v>
+        <v>952000</v>
       </c>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -2484,7 +2496,7 @@
     <row r="110" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <f t="shared" si="4"/>
-        <v>580000</v>
+        <v>952000</v>
       </c>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -2494,7 +2506,7 @@
     <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <f t="shared" si="4"/>
-        <v>580000</v>
+        <v>952000</v>
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -2504,7 +2516,7 @@
     <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <f xml:space="preserve"> A111 +B112-C112</f>
-        <v>580000</v>
+        <v>952000</v>
       </c>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2514,7 +2526,7 @@
     <row r="113" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="8">
         <f>SUM(B93:B112)+B87</f>
-        <v>18455000</v>
+        <v>18827000</v>
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
@@ -2525,7 +2537,7 @@
     <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
-        <v>580000</v>
+        <v>952000</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="148">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -457,6 +457,12 @@
   </si>
   <si>
     <t>سیگار تخمه ژاپنی</t>
+  </si>
+  <si>
+    <t>1405/07/15</t>
+  </si>
+  <si>
+    <t>قهوه سیگار تیغ</t>
   </si>
 </sst>
 </file>
@@ -966,7 +972,7 @@
       </c>
       <c r="H2" s="8">
         <f>C115</f>
-        <v>952000</v>
+        <v>1342000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2476,17 +2482,23 @@
     <row r="108" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <f t="shared" si="4"/>
-        <v>952000</v>
-      </c>
-      <c r="B108" s="7"/>
+        <v>1342000</v>
+      </c>
+      <c r="B108" s="7">
+        <v>390000</v>
+      </c>
       <c r="C108" s="7"/>
-      <c r="D108" s="1"/>
-      <c r="E108" s="1"/>
+      <c r="D108" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="109" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <f t="shared" si="4"/>
-        <v>952000</v>
+        <v>1342000</v>
       </c>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -2496,7 +2508,7 @@
     <row r="110" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <f t="shared" si="4"/>
-        <v>952000</v>
+        <v>1342000</v>
       </c>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -2506,7 +2518,7 @@
     <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <f t="shared" si="4"/>
-        <v>952000</v>
+        <v>1342000</v>
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -2516,7 +2528,7 @@
     <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <f xml:space="preserve"> A111 +B112-C112</f>
-        <v>952000</v>
+        <v>1342000</v>
       </c>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2526,7 +2538,7 @@
     <row r="113" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="8">
         <f>SUM(B93:B112)+B87</f>
-        <v>18827000</v>
+        <v>19217000</v>
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
@@ -2537,7 +2549,7 @@
     <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
-        <v>952000</v>
+        <v>1342000</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="149">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -463,6 +463,9 @@
   </si>
   <si>
     <t>قهوه سیگار تیغ</t>
+  </si>
+  <si>
+    <t>1405/07/16</t>
   </si>
 </sst>
 </file>
@@ -972,7 +975,7 @@
       </c>
       <c r="H2" s="8">
         <f>C115</f>
-        <v>1342000</v>
+        <v>1532000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2498,17 +2501,23 @@
     <row r="109" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <f t="shared" si="4"/>
-        <v>1342000</v>
-      </c>
-      <c r="B109" s="7"/>
+        <v>1532000</v>
+      </c>
+      <c r="B109" s="7">
+        <v>190000</v>
+      </c>
       <c r="C109" s="7"/>
-      <c r="D109" s="1"/>
-      <c r="E109" s="1"/>
+      <c r="D109" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="110" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <f t="shared" si="4"/>
-        <v>1342000</v>
+        <v>1532000</v>
       </c>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -2518,7 +2527,7 @@
     <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <f t="shared" si="4"/>
-        <v>1342000</v>
+        <v>1532000</v>
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -2528,7 +2537,7 @@
     <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <f xml:space="preserve"> A111 +B112-C112</f>
-        <v>1342000</v>
+        <v>1532000</v>
       </c>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2538,7 +2547,7 @@
     <row r="113" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="8">
         <f>SUM(B93:B112)+B87</f>
-        <v>19217000</v>
+        <v>19407000</v>
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
@@ -2549,7 +2558,7 @@
     <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
-        <v>1342000</v>
+        <v>1532000</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="150">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -466,6 +466,9 @@
   </si>
   <si>
     <t>1405/07/16</t>
+  </si>
+  <si>
+    <t>1405/07/19</t>
   </si>
 </sst>
 </file>
@@ -975,7 +978,7 @@
       </c>
       <c r="H2" s="8">
         <f>C115</f>
-        <v>1532000</v>
+        <v>1722000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2517,17 +2520,23 @@
     <row r="110" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <f t="shared" si="4"/>
-        <v>1532000</v>
-      </c>
-      <c r="B110" s="7"/>
+        <v>1722000</v>
+      </c>
+      <c r="B110" s="7">
+        <v>190000</v>
+      </c>
       <c r="C110" s="7"/>
-      <c r="D110" s="1"/>
-      <c r="E110" s="1"/>
+      <c r="D110" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <f t="shared" si="4"/>
-        <v>1532000</v>
+        <v>1722000</v>
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -2537,7 +2546,7 @@
     <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <f xml:space="preserve"> A111 +B112-C112</f>
-        <v>1532000</v>
+        <v>1722000</v>
       </c>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2547,7 +2556,7 @@
     <row r="113" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="8">
         <f>SUM(B93:B112)+B87</f>
-        <v>19407000</v>
+        <v>19597000</v>
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
@@ -2558,7 +2567,7 @@
     <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
-        <v>1532000</v>
+        <v>1722000</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="152">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -469,6 +469,12 @@
   </si>
   <si>
     <t>1405/07/19</t>
+  </si>
+  <si>
+    <t>1405/07/21</t>
+  </si>
+  <si>
+    <t>سیگار قهوه شکلات</t>
   </si>
 </sst>
 </file>
@@ -978,7 +984,7 @@
       </c>
       <c r="H2" s="8">
         <f>C115</f>
-        <v>1722000</v>
+        <v>2115000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2536,17 +2542,23 @@
     <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <f t="shared" si="4"/>
-        <v>1722000</v>
-      </c>
-      <c r="B111" s="7"/>
+        <v>2115000</v>
+      </c>
+      <c r="B111" s="7">
+        <v>393000</v>
+      </c>
       <c r="C111" s="7"/>
-      <c r="D111" s="1"/>
-      <c r="E111" s="1"/>
+      <c r="D111" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <f xml:space="preserve"> A111 +B112-C112</f>
-        <v>1722000</v>
+        <v>2115000</v>
       </c>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2556,7 +2568,7 @@
     <row r="113" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="8">
         <f>SUM(B93:B112)+B87</f>
-        <v>19597000</v>
+        <v>19990000</v>
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
@@ -2567,7 +2579,7 @@
     <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
-        <v>1722000</v>
+        <v>2115000</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="153">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -475,6 +475,9 @@
   </si>
   <si>
     <t>سیگار قهوه شکلات</t>
+  </si>
+  <si>
+    <t>1405/07/22</t>
   </si>
 </sst>
 </file>
@@ -984,7 +987,7 @@
       </c>
       <c r="H2" s="8">
         <f>C115</f>
-        <v>2115000</v>
+        <v>2515000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2558,17 +2561,23 @@
     <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <f xml:space="preserve"> A111 +B112-C112</f>
-        <v>2115000</v>
-      </c>
-      <c r="B112" s="7"/>
+        <v>2515000</v>
+      </c>
+      <c r="B112" s="7">
+        <v>400000</v>
+      </c>
       <c r="C112" s="7"/>
-      <c r="D112" s="1"/>
-      <c r="E112" s="1"/>
+      <c r="D112" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="113" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="8">
         <f>SUM(B93:B112)+B87</f>
-        <v>19990000</v>
+        <v>20390000</v>
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
@@ -2579,7 +2588,7 @@
     <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
-        <v>2115000</v>
+        <v>2515000</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="154">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -478,6 +478,9 @@
   </si>
   <si>
     <t>1405/07/22</t>
+  </si>
+  <si>
+    <t>1405/07/25</t>
   </si>
 </sst>
 </file>
@@ -588,7 +591,35 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="16">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -986,8 +1017,8 @@
         <v>7</v>
       </c>
       <c r="H2" s="8">
-        <f>C115</f>
-        <v>2515000</v>
+        <f>C141</f>
+        <v>2705000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2574,7 +2605,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="113" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="8">
         <f>SUM(B93:B112)+B87</f>
         <v>20390000</v>
@@ -2584,8 +2615,8 @@
         <v>17542000</v>
       </c>
     </row>
-    <row r="114" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
         <v>2515000</v>
@@ -2594,35 +2625,262 @@
         <v>61</v>
       </c>
     </row>
-    <row r="116" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B117" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C117" s="10"/>
+    </row>
+    <row r="118" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B118" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C118" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="7">
+        <f xml:space="preserve"> C115+B119-C119</f>
+        <v>2705000</v>
+      </c>
+      <c r="B119" s="7">
+        <v>190000</v>
+      </c>
+      <c r="C119" s="7"/>
+      <c r="D119" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="7">
+        <f xml:space="preserve"> A119 +B120-C120</f>
+        <v>2705000</v>
+      </c>
+      <c r="B120" s="7"/>
+      <c r="C120" s="7"/>
+      <c r="D120" s="1"/>
+      <c r="E120" s="1"/>
+    </row>
+    <row r="121" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="7">
+        <f t="shared" ref="A121:A137" si="5" xml:space="preserve"> A120 +B121-C121</f>
+        <v>2705000</v>
+      </c>
+      <c r="B121" s="7"/>
+      <c r="C121" s="7"/>
+      <c r="D121" s="1"/>
+      <c r="E121" s="1"/>
+    </row>
+    <row r="122" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="7">
+        <f t="shared" si="5"/>
+        <v>2705000</v>
+      </c>
+      <c r="B122" s="7"/>
+      <c r="C122" s="7"/>
+      <c r="D122" s="1"/>
+      <c r="E122" s="1"/>
+    </row>
+    <row r="123" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="7">
+        <f t="shared" si="5"/>
+        <v>2705000</v>
+      </c>
+      <c r="B123" s="7"/>
+      <c r="C123" s="7"/>
+      <c r="D123" s="1"/>
+      <c r="E123" s="1"/>
+    </row>
+    <row r="124" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="7">
+        <f t="shared" si="5"/>
+        <v>2705000</v>
+      </c>
+      <c r="B124" s="7"/>
+      <c r="C124" s="7"/>
+      <c r="D124" s="1"/>
+      <c r="E124" s="1"/>
+    </row>
+    <row r="125" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="7">
+        <f t="shared" si="5"/>
+        <v>2705000</v>
+      </c>
+      <c r="B125" s="7"/>
+      <c r="C125" s="7"/>
+      <c r="D125" s="1"/>
+      <c r="E125" s="1"/>
+    </row>
+    <row r="126" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="7">
+        <f t="shared" si="5"/>
+        <v>2705000</v>
+      </c>
+      <c r="B126" s="7"/>
+      <c r="C126" s="7"/>
+      <c r="D126" s="1"/>
+      <c r="E126" s="1"/>
+    </row>
+    <row r="127" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="7">
+        <f t="shared" si="5"/>
+        <v>2705000</v>
+      </c>
+      <c r="B127" s="7"/>
+      <c r="C127" s="7"/>
+      <c r="D127" s="1"/>
+      <c r="E127" s="1"/>
+    </row>
+    <row r="128" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="7">
+        <f t="shared" si="5"/>
+        <v>2705000</v>
+      </c>
+      <c r="B128" s="7"/>
+      <c r="C128" s="7"/>
+      <c r="D128" s="1"/>
+      <c r="E128" s="1"/>
+    </row>
+    <row r="129" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="7">
+        <f t="shared" si="5"/>
+        <v>2705000</v>
+      </c>
+      <c r="B129" s="7"/>
+      <c r="C129" s="7"/>
+      <c r="D129" s="1"/>
+      <c r="E129" s="1"/>
+    </row>
+    <row r="130" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="7">
+        <f t="shared" si="5"/>
+        <v>2705000</v>
+      </c>
+      <c r="B130" s="7"/>
+      <c r="C130" s="7"/>
+      <c r="D130" s="1"/>
+      <c r="E130" s="1"/>
+    </row>
+    <row r="131" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="7">
+        <f t="shared" si="5"/>
+        <v>2705000</v>
+      </c>
+      <c r="B131" s="7"/>
+      <c r="C131" s="7"/>
+      <c r="D131" s="1"/>
+      <c r="E131" s="1"/>
+    </row>
+    <row r="132" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="7">
+        <f t="shared" si="5"/>
+        <v>2705000</v>
+      </c>
+      <c r="B132" s="7"/>
+      <c r="C132" s="7"/>
+      <c r="D132" s="1"/>
+      <c r="E132" s="1"/>
+    </row>
+    <row r="133" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="7">
+        <f t="shared" si="5"/>
+        <v>2705000</v>
+      </c>
+      <c r="B133" s="7"/>
+      <c r="C133" s="7"/>
+      <c r="D133" s="1"/>
+      <c r="E133" s="1"/>
+    </row>
+    <row r="134" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="7">
+        <f t="shared" si="5"/>
+        <v>2705000</v>
+      </c>
+      <c r="B134" s="7"/>
+      <c r="C134" s="7"/>
+      <c r="D134" s="1"/>
+      <c r="E134" s="1"/>
+    </row>
+    <row r="135" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="7">
+        <f t="shared" si="5"/>
+        <v>2705000</v>
+      </c>
+      <c r="B135" s="7"/>
+      <c r="C135" s="7"/>
+      <c r="D135" s="1"/>
+      <c r="E135" s="1"/>
+    </row>
+    <row r="136" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="7">
+        <f t="shared" si="5"/>
+        <v>2705000</v>
+      </c>
+      <c r="B136" s="7"/>
+      <c r="C136" s="7"/>
+      <c r="D136" s="1"/>
+      <c r="E136" s="1"/>
+    </row>
+    <row r="137" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="7">
+        <f t="shared" si="5"/>
+        <v>2705000</v>
+      </c>
+      <c r="B137" s="7"/>
+      <c r="C137" s="7"/>
+      <c r="D137" s="1"/>
+      <c r="E137" s="1"/>
+    </row>
+    <row r="138" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="7">
+        <f xml:space="preserve"> A137 +B138-C138</f>
+        <v>2705000</v>
+      </c>
+      <c r="B138" s="7"/>
+      <c r="C138" s="7"/>
+      <c r="D138" s="1"/>
+      <c r="E138" s="1"/>
+    </row>
+    <row r="139" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B139" s="8">
+        <f>SUM(B119:B138)+B113</f>
+        <v>20580000</v>
+      </c>
+      <c r="C139" s="8">
+        <f>SUM(C119:C138)+C113</f>
+        <v>17542000</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C141" s="13">
+        <f>A138</f>
+        <v>2705000</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="145" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="146" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="147" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2630,20 +2888,34 @@
     <row r="149" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <conditionalFormatting sqref="C62">
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="16" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="15" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C89">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="10" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="12" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C115">
     <cfRule type="cellIs" dxfId="7" priority="5" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -2657,7 +2929,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C115">
+  <conditionalFormatting sqref="C141">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="155">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -481,6 +481,9 @@
   </si>
   <si>
     <t>1405/07/25</t>
+  </si>
+  <si>
+    <t>1405/07/27</t>
   </si>
 </sst>
 </file>
@@ -1018,7 +1021,7 @@
       </c>
       <c r="H2" s="8">
         <f>C141</f>
-        <v>2705000</v>
+        <v>1895000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2671,27 +2674,39 @@
     <row r="120" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="7">
         <f xml:space="preserve"> A119 +B120-C120</f>
-        <v>2705000</v>
+        <v>1705000</v>
       </c>
       <c r="B120" s="7"/>
-      <c r="C120" s="7"/>
-      <c r="D120" s="1"/>
-      <c r="E120" s="1"/>
+      <c r="C120" s="7">
+        <v>1000000</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="121" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="7">
         <f t="shared" ref="A121:A137" si="5" xml:space="preserve"> A120 +B121-C121</f>
-        <v>2705000</v>
-      </c>
-      <c r="B121" s="7"/>
+        <v>1895000</v>
+      </c>
+      <c r="B121" s="7">
+        <v>190000</v>
+      </c>
       <c r="C121" s="7"/>
-      <c r="D121" s="1"/>
-      <c r="E121" s="1"/>
+      <c r="D121" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="122" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="7">
         <f t="shared" si="5"/>
-        <v>2705000</v>
+        <v>1895000</v>
       </c>
       <c r="B122" s="7"/>
       <c r="C122" s="7"/>
@@ -2701,7 +2716,7 @@
     <row r="123" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="7">
         <f t="shared" si="5"/>
-        <v>2705000</v>
+        <v>1895000</v>
       </c>
       <c r="B123" s="7"/>
       <c r="C123" s="7"/>
@@ -2711,7 +2726,7 @@
     <row r="124" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="7">
         <f t="shared" si="5"/>
-        <v>2705000</v>
+        <v>1895000</v>
       </c>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -2721,7 +2736,7 @@
     <row r="125" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="7">
         <f t="shared" si="5"/>
-        <v>2705000</v>
+        <v>1895000</v>
       </c>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -2731,7 +2746,7 @@
     <row r="126" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="7">
         <f t="shared" si="5"/>
-        <v>2705000</v>
+        <v>1895000</v>
       </c>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -2741,7 +2756,7 @@
     <row r="127" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="7">
         <f t="shared" si="5"/>
-        <v>2705000</v>
+        <v>1895000</v>
       </c>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -2751,7 +2766,7 @@
     <row r="128" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="7">
         <f t="shared" si="5"/>
-        <v>2705000</v>
+        <v>1895000</v>
       </c>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -2761,7 +2776,7 @@
     <row r="129" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="7">
         <f t="shared" si="5"/>
-        <v>2705000</v>
+        <v>1895000</v>
       </c>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -2771,7 +2786,7 @@
     <row r="130" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="7">
         <f t="shared" si="5"/>
-        <v>2705000</v>
+        <v>1895000</v>
       </c>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -2781,7 +2796,7 @@
     <row r="131" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="7">
         <f t="shared" si="5"/>
-        <v>2705000</v>
+        <v>1895000</v>
       </c>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -2791,7 +2806,7 @@
     <row r="132" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="7">
         <f t="shared" si="5"/>
-        <v>2705000</v>
+        <v>1895000</v>
       </c>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -2801,7 +2816,7 @@
     <row r="133" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="7">
         <f t="shared" si="5"/>
-        <v>2705000</v>
+        <v>1895000</v>
       </c>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -2811,7 +2826,7 @@
     <row r="134" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="7">
         <f t="shared" si="5"/>
-        <v>2705000</v>
+        <v>1895000</v>
       </c>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -2821,7 +2836,7 @@
     <row r="135" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="7">
         <f t="shared" si="5"/>
-        <v>2705000</v>
+        <v>1895000</v>
       </c>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -2831,7 +2846,7 @@
     <row r="136" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="7">
         <f t="shared" si="5"/>
-        <v>2705000</v>
+        <v>1895000</v>
       </c>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -2841,7 +2856,7 @@
     <row r="137" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="7">
         <f t="shared" si="5"/>
-        <v>2705000</v>
+        <v>1895000</v>
       </c>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -2851,7 +2866,7 @@
     <row r="138" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="7">
         <f xml:space="preserve"> A137 +B138-C138</f>
-        <v>2705000</v>
+        <v>1895000</v>
       </c>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -2861,18 +2876,18 @@
     <row r="139" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B139" s="8">
         <f>SUM(B119:B138)+B113</f>
-        <v>20580000</v>
+        <v>20770000</v>
       </c>
       <c r="C139" s="8">
         <f>SUM(C119:C138)+C113</f>
-        <v>17542000</v>
+        <v>18542000</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="141" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C141" s="13">
         <f>A138</f>
-        <v>2705000</v>
+        <v>1895000</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="157">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -484,6 +484,12 @@
   </si>
   <si>
     <t>1405/07/27</t>
+  </si>
+  <si>
+    <t>1405/07/28</t>
+  </si>
+  <si>
+    <t>نخوچی بادام زمینی</t>
   </si>
 </sst>
 </file>
@@ -1021,7 +1027,7 @@
       </c>
       <c r="H2" s="8">
         <f>C141</f>
-        <v>1895000</v>
+        <v>2651000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2706,17 +2712,23 @@
     <row r="122" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="7">
         <f t="shared" si="5"/>
-        <v>1895000</v>
-      </c>
-      <c r="B122" s="7"/>
+        <v>2651000</v>
+      </c>
+      <c r="B122" s="7">
+        <v>756000</v>
+      </c>
       <c r="C122" s="7"/>
-      <c r="D122" s="1"/>
-      <c r="E122" s="1"/>
+      <c r="D122" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="123" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="7">
         <f t="shared" si="5"/>
-        <v>1895000</v>
+        <v>2651000</v>
       </c>
       <c r="B123" s="7"/>
       <c r="C123" s="7"/>
@@ -2726,7 +2738,7 @@
     <row r="124" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="7">
         <f t="shared" si="5"/>
-        <v>1895000</v>
+        <v>2651000</v>
       </c>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -2736,7 +2748,7 @@
     <row r="125" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="7">
         <f t="shared" si="5"/>
-        <v>1895000</v>
+        <v>2651000</v>
       </c>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -2746,7 +2758,7 @@
     <row r="126" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="7">
         <f t="shared" si="5"/>
-        <v>1895000</v>
+        <v>2651000</v>
       </c>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -2756,7 +2768,7 @@
     <row r="127" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="7">
         <f t="shared" si="5"/>
-        <v>1895000</v>
+        <v>2651000</v>
       </c>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -2766,7 +2778,7 @@
     <row r="128" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="7">
         <f t="shared" si="5"/>
-        <v>1895000</v>
+        <v>2651000</v>
       </c>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -2776,7 +2788,7 @@
     <row r="129" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="7">
         <f t="shared" si="5"/>
-        <v>1895000</v>
+        <v>2651000</v>
       </c>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -2786,7 +2798,7 @@
     <row r="130" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="7">
         <f t="shared" si="5"/>
-        <v>1895000</v>
+        <v>2651000</v>
       </c>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -2796,7 +2808,7 @@
     <row r="131" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="7">
         <f t="shared" si="5"/>
-        <v>1895000</v>
+        <v>2651000</v>
       </c>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -2806,7 +2818,7 @@
     <row r="132" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="7">
         <f t="shared" si="5"/>
-        <v>1895000</v>
+        <v>2651000</v>
       </c>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -2816,7 +2828,7 @@
     <row r="133" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="7">
         <f t="shared" si="5"/>
-        <v>1895000</v>
+        <v>2651000</v>
       </c>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -2826,7 +2838,7 @@
     <row r="134" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="7">
         <f t="shared" si="5"/>
-        <v>1895000</v>
+        <v>2651000</v>
       </c>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -2836,7 +2848,7 @@
     <row r="135" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="7">
         <f t="shared" si="5"/>
-        <v>1895000</v>
+        <v>2651000</v>
       </c>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -2846,7 +2858,7 @@
     <row r="136" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="7">
         <f t="shared" si="5"/>
-        <v>1895000</v>
+        <v>2651000</v>
       </c>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -2856,7 +2868,7 @@
     <row r="137" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="7">
         <f t="shared" si="5"/>
-        <v>1895000</v>
+        <v>2651000</v>
       </c>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -2866,7 +2878,7 @@
     <row r="138" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="7">
         <f xml:space="preserve"> A137 +B138-C138</f>
-        <v>1895000</v>
+        <v>2651000</v>
       </c>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -2876,7 +2888,7 @@
     <row r="139" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B139" s="8">
         <f>SUM(B119:B138)+B113</f>
-        <v>20770000</v>
+        <v>21526000</v>
       </c>
       <c r="C139" s="8">
         <f>SUM(C119:C138)+C113</f>
@@ -2887,7 +2899,7 @@
     <row r="141" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C141" s="13">
         <f>A138</f>
-        <v>1895000</v>
+        <v>2651000</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="158">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -490,6 +490,9 @@
   </si>
   <si>
     <t>نخوچی بادام زمینی</t>
+  </si>
+  <si>
+    <t>1405/08/01</t>
   </si>
 </sst>
 </file>
@@ -1027,7 +1030,7 @@
       </c>
       <c r="H2" s="8">
         <f>C141</f>
-        <v>2651000</v>
+        <v>2841000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2728,17 +2731,23 @@
     <row r="123" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="7">
         <f t="shared" si="5"/>
-        <v>2651000</v>
-      </c>
-      <c r="B123" s="7"/>
+        <v>2841000</v>
+      </c>
+      <c r="B123" s="7">
+        <v>190000</v>
+      </c>
       <c r="C123" s="7"/>
-      <c r="D123" s="1"/>
-      <c r="E123" s="1"/>
+      <c r="D123" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="124" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="7">
         <f t="shared" si="5"/>
-        <v>2651000</v>
+        <v>2841000</v>
       </c>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -2748,7 +2757,7 @@
     <row r="125" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="7">
         <f t="shared" si="5"/>
-        <v>2651000</v>
+        <v>2841000</v>
       </c>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -2758,7 +2767,7 @@
     <row r="126" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="7">
         <f t="shared" si="5"/>
-        <v>2651000</v>
+        <v>2841000</v>
       </c>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -2768,7 +2777,7 @@
     <row r="127" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="7">
         <f t="shared" si="5"/>
-        <v>2651000</v>
+        <v>2841000</v>
       </c>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -2778,7 +2787,7 @@
     <row r="128" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="7">
         <f t="shared" si="5"/>
-        <v>2651000</v>
+        <v>2841000</v>
       </c>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -2788,7 +2797,7 @@
     <row r="129" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="7">
         <f t="shared" si="5"/>
-        <v>2651000</v>
+        <v>2841000</v>
       </c>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -2798,7 +2807,7 @@
     <row r="130" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="7">
         <f t="shared" si="5"/>
-        <v>2651000</v>
+        <v>2841000</v>
       </c>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -2808,7 +2817,7 @@
     <row r="131" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="7">
         <f t="shared" si="5"/>
-        <v>2651000</v>
+        <v>2841000</v>
       </c>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -2818,7 +2827,7 @@
     <row r="132" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="7">
         <f t="shared" si="5"/>
-        <v>2651000</v>
+        <v>2841000</v>
       </c>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -2828,7 +2837,7 @@
     <row r="133" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="7">
         <f t="shared" si="5"/>
-        <v>2651000</v>
+        <v>2841000</v>
       </c>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -2838,7 +2847,7 @@
     <row r="134" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="7">
         <f t="shared" si="5"/>
-        <v>2651000</v>
+        <v>2841000</v>
       </c>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -2848,7 +2857,7 @@
     <row r="135" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="7">
         <f t="shared" si="5"/>
-        <v>2651000</v>
+        <v>2841000</v>
       </c>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -2858,7 +2867,7 @@
     <row r="136" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="7">
         <f t="shared" si="5"/>
-        <v>2651000</v>
+        <v>2841000</v>
       </c>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -2868,7 +2877,7 @@
     <row r="137" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="7">
         <f t="shared" si="5"/>
-        <v>2651000</v>
+        <v>2841000</v>
       </c>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -2878,7 +2887,7 @@
     <row r="138" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="7">
         <f xml:space="preserve"> A137 +B138-C138</f>
-        <v>2651000</v>
+        <v>2841000</v>
       </c>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -2888,7 +2897,7 @@
     <row r="139" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B139" s="8">
         <f>SUM(B119:B138)+B113</f>
-        <v>21526000</v>
+        <v>21716000</v>
       </c>
       <c r="C139" s="8">
         <f>SUM(C119:C138)+C113</f>
@@ -2899,7 +2908,7 @@
     <row r="141" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C141" s="13">
         <f>A138</f>
-        <v>2651000</v>
+        <v>2841000</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="159">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -493,6 +493,9 @@
   </si>
   <si>
     <t>1405/08/01</t>
+  </si>
+  <si>
+    <t>1405/08/02</t>
   </si>
 </sst>
 </file>
@@ -1030,7 +1033,7 @@
       </c>
       <c r="H2" s="8">
         <f>C141</f>
-        <v>2841000</v>
+        <v>3056000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2747,17 +2750,23 @@
     <row r="124" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="7">
         <f t="shared" si="5"/>
-        <v>2841000</v>
-      </c>
-      <c r="B124" s="7"/>
+        <v>3056000</v>
+      </c>
+      <c r="B124" s="7">
+        <v>215000</v>
+      </c>
       <c r="C124" s="7"/>
-      <c r="D124" s="1"/>
-      <c r="E124" s="1"/>
+      <c r="D124" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="125" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="7">
         <f t="shared" si="5"/>
-        <v>2841000</v>
+        <v>3056000</v>
       </c>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -2767,7 +2776,7 @@
     <row r="126" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="7">
         <f t="shared" si="5"/>
-        <v>2841000</v>
+        <v>3056000</v>
       </c>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -2777,7 +2786,7 @@
     <row r="127" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="7">
         <f t="shared" si="5"/>
-        <v>2841000</v>
+        <v>3056000</v>
       </c>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -2787,7 +2796,7 @@
     <row r="128" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="7">
         <f t="shared" si="5"/>
-        <v>2841000</v>
+        <v>3056000</v>
       </c>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -2797,7 +2806,7 @@
     <row r="129" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="7">
         <f t="shared" si="5"/>
-        <v>2841000</v>
+        <v>3056000</v>
       </c>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -2807,7 +2816,7 @@
     <row r="130" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="7">
         <f t="shared" si="5"/>
-        <v>2841000</v>
+        <v>3056000</v>
       </c>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -2817,7 +2826,7 @@
     <row r="131" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="7">
         <f t="shared" si="5"/>
-        <v>2841000</v>
+        <v>3056000</v>
       </c>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -2827,7 +2836,7 @@
     <row r="132" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="7">
         <f t="shared" si="5"/>
-        <v>2841000</v>
+        <v>3056000</v>
       </c>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -2837,7 +2846,7 @@
     <row r="133" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="7">
         <f t="shared" si="5"/>
-        <v>2841000</v>
+        <v>3056000</v>
       </c>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -2847,7 +2856,7 @@
     <row r="134" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="7">
         <f t="shared" si="5"/>
-        <v>2841000</v>
+        <v>3056000</v>
       </c>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -2857,7 +2866,7 @@
     <row r="135" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="7">
         <f t="shared" si="5"/>
-        <v>2841000</v>
+        <v>3056000</v>
       </c>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -2867,7 +2876,7 @@
     <row r="136" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="7">
         <f t="shared" si="5"/>
-        <v>2841000</v>
+        <v>3056000</v>
       </c>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -2877,7 +2886,7 @@
     <row r="137" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="7">
         <f t="shared" si="5"/>
-        <v>2841000</v>
+        <v>3056000</v>
       </c>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -2887,7 +2896,7 @@
     <row r="138" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="7">
         <f xml:space="preserve"> A137 +B138-C138</f>
-        <v>2841000</v>
+        <v>3056000</v>
       </c>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -2897,7 +2906,7 @@
     <row r="139" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B139" s="8">
         <f>SUM(B119:B138)+B113</f>
-        <v>21716000</v>
+        <v>21931000</v>
       </c>
       <c r="C139" s="8">
         <f>SUM(C119:C138)+C113</f>
@@ -2908,7 +2917,7 @@
     <row r="141" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C141" s="13">
         <f>A138</f>
-        <v>2841000</v>
+        <v>3056000</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="160">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -496,6 +496,9 @@
   </si>
   <si>
     <t>1405/08/02</t>
+  </si>
+  <si>
+    <t>1405/08/03</t>
   </si>
 </sst>
 </file>
@@ -584,7 +587,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -602,6 +605,36 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1033,7 +1066,7 @@
       </c>
       <c r="H2" s="8">
         <f>C141</f>
-        <v>3056000</v>
+        <v>3151000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2641,289 +2674,315 @@
       </c>
     </row>
     <row r="116" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="8" t="s">
+    <row r="117" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B117" s="10" t="s">
+      <c r="B117" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C117" s="10"/>
-    </row>
-    <row r="118" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="11" t="s">
+      <c r="C117" s="18"/>
+      <c r="D117" s="19"/>
+      <c r="E117" s="19"/>
+    </row>
+    <row r="118" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B118" s="12" t="s">
+      <c r="B118" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="C118" s="11" t="s">
+      <c r="C118" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D118" s="5" t="s">
+      <c r="D118" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="E118" s="5" t="s">
+      <c r="E118" s="22" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="7">
+      <c r="A119" s="23">
         <f xml:space="preserve"> C115+B119-C119</f>
         <v>2705000</v>
       </c>
-      <c r="B119" s="7">
+      <c r="B119" s="23">
         <v>190000</v>
       </c>
-      <c r="C119" s="7"/>
-      <c r="D119" s="1" t="s">
+      <c r="C119" s="23"/>
+      <c r="D119" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="E119" s="1" t="s">
+      <c r="E119" s="24" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="7">
+      <c r="A120" s="23">
         <f xml:space="preserve"> A119 +B120-C120</f>
         <v>1705000</v>
       </c>
-      <c r="B120" s="7"/>
-      <c r="C120" s="7">
+      <c r="B120" s="23"/>
+      <c r="C120" s="23">
         <v>1000000</v>
       </c>
-      <c r="D120" s="1" t="s">
+      <c r="D120" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E120" s="1" t="s">
+      <c r="E120" s="24" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="7">
+      <c r="A121" s="23">
         <f t="shared" ref="A121:A137" si="5" xml:space="preserve"> A120 +B121-C121</f>
         <v>1895000</v>
       </c>
-      <c r="B121" s="7">
+      <c r="B121" s="23">
         <v>190000</v>
       </c>
-      <c r="C121" s="7"/>
-      <c r="D121" s="1" t="s">
+      <c r="C121" s="23"/>
+      <c r="D121" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="E121" s="1" t="s">
+      <c r="E121" s="24" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="7">
+      <c r="A122" s="23">
         <f t="shared" si="5"/>
         <v>2651000</v>
       </c>
-      <c r="B122" s="7">
+      <c r="B122" s="23">
         <v>756000</v>
       </c>
-      <c r="C122" s="7"/>
-      <c r="D122" s="1" t="s">
+      <c r="C122" s="23"/>
+      <c r="D122" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="E122" s="1" t="s">
+      <c r="E122" s="24" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="7">
+      <c r="A123" s="23">
         <f t="shared" si="5"/>
         <v>2841000</v>
       </c>
-      <c r="B123" s="7">
+      <c r="B123" s="23">
         <v>190000</v>
       </c>
-      <c r="C123" s="7"/>
-      <c r="D123" s="1" t="s">
+      <c r="C123" s="23"/>
+      <c r="D123" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="E123" s="1" t="s">
+      <c r="E123" s="24" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="7">
+      <c r="A124" s="23">
         <f t="shared" si="5"/>
         <v>3056000</v>
       </c>
-      <c r="B124" s="7">
+      <c r="B124" s="23">
         <v>215000</v>
       </c>
-      <c r="C124" s="7"/>
-      <c r="D124" s="1" t="s">
+      <c r="C124" s="23"/>
+      <c r="D124" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="E124" s="1" t="s">
+      <c r="E124" s="24" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="7">
+      <c r="A125" s="23">
         <f t="shared" si="5"/>
-        <v>3056000</v>
-      </c>
-      <c r="B125" s="7"/>
-      <c r="C125" s="7"/>
-      <c r="D125" s="1"/>
-      <c r="E125" s="1"/>
+        <v>3151000</v>
+      </c>
+      <c r="B125" s="23">
+        <v>95000</v>
+      </c>
+      <c r="C125" s="23"/>
+      <c r="D125" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="E125" s="24" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="126" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="7">
+      <c r="A126" s="23">
         <f t="shared" si="5"/>
-        <v>3056000</v>
-      </c>
-      <c r="B126" s="7"/>
-      <c r="C126" s="7"/>
-      <c r="D126" s="1"/>
-      <c r="E126" s="1"/>
+        <v>3151000</v>
+      </c>
+      <c r="B126" s="23"/>
+      <c r="C126" s="23"/>
+      <c r="D126" s="24"/>
+      <c r="E126" s="24"/>
     </row>
     <row r="127" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="7">
+      <c r="A127" s="23">
         <f t="shared" si="5"/>
-        <v>3056000</v>
-      </c>
-      <c r="B127" s="7"/>
-      <c r="C127" s="7"/>
-      <c r="D127" s="1"/>
-      <c r="E127" s="1"/>
+        <v>3151000</v>
+      </c>
+      <c r="B127" s="23"/>
+      <c r="C127" s="23"/>
+      <c r="D127" s="24"/>
+      <c r="E127" s="24"/>
     </row>
     <row r="128" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="7">
+      <c r="A128" s="23">
         <f t="shared" si="5"/>
-        <v>3056000</v>
-      </c>
-      <c r="B128" s="7"/>
-      <c r="C128" s="7"/>
-      <c r="D128" s="1"/>
-      <c r="E128" s="1"/>
+        <v>3151000</v>
+      </c>
+      <c r="B128" s="23"/>
+      <c r="C128" s="23"/>
+      <c r="D128" s="24"/>
+      <c r="E128" s="24"/>
     </row>
     <row r="129" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="7">
+      <c r="A129" s="23">
         <f t="shared" si="5"/>
-        <v>3056000</v>
-      </c>
-      <c r="B129" s="7"/>
-      <c r="C129" s="7"/>
-      <c r="D129" s="1"/>
-      <c r="E129" s="1"/>
+        <v>3151000</v>
+      </c>
+      <c r="B129" s="23"/>
+      <c r="C129" s="23"/>
+      <c r="D129" s="24"/>
+      <c r="E129" s="24"/>
     </row>
     <row r="130" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="7">
+      <c r="A130" s="23">
         <f t="shared" si="5"/>
-        <v>3056000</v>
-      </c>
-      <c r="B130" s="7"/>
-      <c r="C130" s="7"/>
-      <c r="D130" s="1"/>
-      <c r="E130" s="1"/>
+        <v>3151000</v>
+      </c>
+      <c r="B130" s="23"/>
+      <c r="C130" s="23"/>
+      <c r="D130" s="24"/>
+      <c r="E130" s="24"/>
     </row>
     <row r="131" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="7">
+      <c r="A131" s="23">
         <f t="shared" si="5"/>
-        <v>3056000</v>
-      </c>
-      <c r="B131" s="7"/>
-      <c r="C131" s="7"/>
-      <c r="D131" s="1"/>
-      <c r="E131" s="1"/>
+        <v>3151000</v>
+      </c>
+      <c r="B131" s="23"/>
+      <c r="C131" s="23"/>
+      <c r="D131" s="24"/>
+      <c r="E131" s="24"/>
     </row>
     <row r="132" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="7">
+      <c r="A132" s="23">
         <f t="shared" si="5"/>
-        <v>3056000</v>
-      </c>
-      <c r="B132" s="7"/>
-      <c r="C132" s="7"/>
-      <c r="D132" s="1"/>
-      <c r="E132" s="1"/>
+        <v>3151000</v>
+      </c>
+      <c r="B132" s="23"/>
+      <c r="C132" s="23"/>
+      <c r="D132" s="24"/>
+      <c r="E132" s="24"/>
     </row>
     <row r="133" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="7">
+      <c r="A133" s="23">
         <f t="shared" si="5"/>
-        <v>3056000</v>
-      </c>
-      <c r="B133" s="7"/>
-      <c r="C133" s="7"/>
-      <c r="D133" s="1"/>
-      <c r="E133" s="1"/>
+        <v>3151000</v>
+      </c>
+      <c r="B133" s="23"/>
+      <c r="C133" s="23"/>
+      <c r="D133" s="24"/>
+      <c r="E133" s="24"/>
     </row>
     <row r="134" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="7">
+      <c r="A134" s="23">
         <f t="shared" si="5"/>
-        <v>3056000</v>
-      </c>
-      <c r="B134" s="7"/>
-      <c r="C134" s="7"/>
-      <c r="D134" s="1"/>
-      <c r="E134" s="1"/>
+        <v>3151000</v>
+      </c>
+      <c r="B134" s="23"/>
+      <c r="C134" s="23"/>
+      <c r="D134" s="24"/>
+      <c r="E134" s="24"/>
     </row>
     <row r="135" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="7">
+      <c r="A135" s="23">
         <f t="shared" si="5"/>
-        <v>3056000</v>
-      </c>
-      <c r="B135" s="7"/>
-      <c r="C135" s="7"/>
-      <c r="D135" s="1"/>
-      <c r="E135" s="1"/>
+        <v>3151000</v>
+      </c>
+      <c r="B135" s="23"/>
+      <c r="C135" s="23"/>
+      <c r="D135" s="24"/>
+      <c r="E135" s="24"/>
     </row>
     <row r="136" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="7">
+      <c r="A136" s="23">
         <f t="shared" si="5"/>
-        <v>3056000</v>
-      </c>
-      <c r="B136" s="7"/>
-      <c r="C136" s="7"/>
-      <c r="D136" s="1"/>
-      <c r="E136" s="1"/>
+        <v>3151000</v>
+      </c>
+      <c r="B136" s="23"/>
+      <c r="C136" s="23"/>
+      <c r="D136" s="24"/>
+      <c r="E136" s="24"/>
     </row>
     <row r="137" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="7">
+      <c r="A137" s="23">
         <f t="shared" si="5"/>
-        <v>3056000</v>
-      </c>
-      <c r="B137" s="7"/>
-      <c r="C137" s="7"/>
-      <c r="D137" s="1"/>
-      <c r="E137" s="1"/>
+        <v>3151000</v>
+      </c>
+      <c r="B137" s="23"/>
+      <c r="C137" s="23"/>
+      <c r="D137" s="24"/>
+      <c r="E137" s="24"/>
     </row>
     <row r="138" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="7">
+      <c r="A138" s="23">
         <f xml:space="preserve"> A137 +B138-C138</f>
-        <v>3056000</v>
-      </c>
-      <c r="B138" s="7"/>
-      <c r="C138" s="7"/>
-      <c r="D138" s="1"/>
-      <c r="E138" s="1"/>
+        <v>3151000</v>
+      </c>
+      <c r="B138" s="23"/>
+      <c r="C138" s="23"/>
+      <c r="D138" s="24"/>
+      <c r="E138" s="24"/>
     </row>
     <row r="139" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B139" s="8">
+      <c r="A139" s="19"/>
+      <c r="B139" s="17">
         <f>SUM(B119:B138)+B113</f>
-        <v>21931000</v>
-      </c>
-      <c r="C139" s="8">
+        <v>22026000</v>
+      </c>
+      <c r="C139" s="17">
         <f>SUM(C119:C138)+C113</f>
         <v>18542000</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C141" s="13">
+      <c r="D139" s="19"/>
+      <c r="E139" s="19"/>
+    </row>
+    <row r="140" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="19"/>
+      <c r="B140" s="19"/>
+      <c r="C140" s="19"/>
+      <c r="D140" s="19"/>
+      <c r="E140" s="19"/>
+    </row>
+    <row r="141" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="19"/>
+      <c r="B141" s="19"/>
+      <c r="C141" s="25">
         <f>A138</f>
-        <v>3056000</v>
-      </c>
-      <c r="D141" s="2" t="s">
+        <v>3151000</v>
+      </c>
+      <c r="D141" s="26" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="E141" s="19"/>
+    </row>
+    <row r="142" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="19"/>
+      <c r="B142" s="19"/>
+      <c r="C142" s="19"/>
+      <c r="D142" s="19"/>
+      <c r="E142" s="19"/>
+    </row>
     <row r="143" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="144" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="145" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="162">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -499,6 +499,12 @@
   </si>
   <si>
     <t>1405/08/03</t>
+  </si>
+  <si>
+    <t>1405/09/03</t>
+  </si>
+  <si>
+    <t>سیگار شکلات تخمه</t>
   </si>
 </sst>
 </file>
@@ -1066,7 +1072,7 @@
       </c>
       <c r="H2" s="8">
         <f>C141</f>
-        <v>3151000</v>
+        <v>3916000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2817,17 +2823,23 @@
     <row r="126" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="23">
         <f t="shared" si="5"/>
-        <v>3151000</v>
-      </c>
-      <c r="B126" s="23"/>
+        <v>3916000</v>
+      </c>
+      <c r="B126" s="23">
+        <v>765000</v>
+      </c>
       <c r="C126" s="23"/>
-      <c r="D126" s="24"/>
-      <c r="E126" s="24"/>
+      <c r="D126" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E126" s="24" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="127" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="23">
         <f t="shared" si="5"/>
-        <v>3151000</v>
+        <v>3916000</v>
       </c>
       <c r="B127" s="23"/>
       <c r="C127" s="23"/>
@@ -2837,7 +2849,7 @@
     <row r="128" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="23">
         <f t="shared" si="5"/>
-        <v>3151000</v>
+        <v>3916000</v>
       </c>
       <c r="B128" s="23"/>
       <c r="C128" s="23"/>
@@ -2847,7 +2859,7 @@
     <row r="129" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="23">
         <f t="shared" si="5"/>
-        <v>3151000</v>
+        <v>3916000</v>
       </c>
       <c r="B129" s="23"/>
       <c r="C129" s="23"/>
@@ -2857,7 +2869,7 @@
     <row r="130" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="23">
         <f t="shared" si="5"/>
-        <v>3151000</v>
+        <v>3916000</v>
       </c>
       <c r="B130" s="23"/>
       <c r="C130" s="23"/>
@@ -2867,7 +2879,7 @@
     <row r="131" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="23">
         <f t="shared" si="5"/>
-        <v>3151000</v>
+        <v>3916000</v>
       </c>
       <c r="B131" s="23"/>
       <c r="C131" s="23"/>
@@ -2877,7 +2889,7 @@
     <row r="132" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="23">
         <f t="shared" si="5"/>
-        <v>3151000</v>
+        <v>3916000</v>
       </c>
       <c r="B132" s="23"/>
       <c r="C132" s="23"/>
@@ -2887,7 +2899,7 @@
     <row r="133" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="23">
         <f t="shared" si="5"/>
-        <v>3151000</v>
+        <v>3916000</v>
       </c>
       <c r="B133" s="23"/>
       <c r="C133" s="23"/>
@@ -2897,7 +2909,7 @@
     <row r="134" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="23">
         <f t="shared" si="5"/>
-        <v>3151000</v>
+        <v>3916000</v>
       </c>
       <c r="B134" s="23"/>
       <c r="C134" s="23"/>
@@ -2907,7 +2919,7 @@
     <row r="135" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="23">
         <f t="shared" si="5"/>
-        <v>3151000</v>
+        <v>3916000</v>
       </c>
       <c r="B135" s="23"/>
       <c r="C135" s="23"/>
@@ -2917,7 +2929,7 @@
     <row r="136" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="23">
         <f t="shared" si="5"/>
-        <v>3151000</v>
+        <v>3916000</v>
       </c>
       <c r="B136" s="23"/>
       <c r="C136" s="23"/>
@@ -2927,7 +2939,7 @@
     <row r="137" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="23">
         <f t="shared" si="5"/>
-        <v>3151000</v>
+        <v>3916000</v>
       </c>
       <c r="B137" s="23"/>
       <c r="C137" s="23"/>
@@ -2937,7 +2949,7 @@
     <row r="138" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="23">
         <f xml:space="preserve"> A137 +B138-C138</f>
-        <v>3151000</v>
+        <v>3916000</v>
       </c>
       <c r="B138" s="23"/>
       <c r="C138" s="23"/>
@@ -2948,7 +2960,7 @@
       <c r="A139" s="19"/>
       <c r="B139" s="17">
         <f>SUM(B119:B138)+B113</f>
-        <v>22026000</v>
+        <v>22791000</v>
       </c>
       <c r="C139" s="17">
         <f>SUM(C119:C138)+C113</f>
@@ -2969,7 +2981,7 @@
       <c r="B141" s="19"/>
       <c r="C141" s="25">
         <f>A138</f>
-        <v>3151000</v>
+        <v>3916000</v>
       </c>
       <c r="D141" s="26" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="163">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -505,6 +505,9 @@
   </si>
   <si>
     <t>سیگار شکلات تخمه</t>
+  </si>
+  <si>
+    <t>1405/08/06</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1075,7 @@
       </c>
       <c r="H2" s="8">
         <f>C141</f>
-        <v>3916000</v>
+        <v>4106000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2839,17 +2842,23 @@
     <row r="127" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="23">
         <f t="shared" si="5"/>
-        <v>3916000</v>
-      </c>
-      <c r="B127" s="23"/>
+        <v>4106000</v>
+      </c>
+      <c r="B127" s="23">
+        <v>190000</v>
+      </c>
       <c r="C127" s="23"/>
-      <c r="D127" s="24"/>
-      <c r="E127" s="24"/>
+      <c r="D127" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="E127" s="24" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="128" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="23">
         <f t="shared" si="5"/>
-        <v>3916000</v>
+        <v>4106000</v>
       </c>
       <c r="B128" s="23"/>
       <c r="C128" s="23"/>
@@ -2859,7 +2868,7 @@
     <row r="129" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="23">
         <f t="shared" si="5"/>
-        <v>3916000</v>
+        <v>4106000</v>
       </c>
       <c r="B129" s="23"/>
       <c r="C129" s="23"/>
@@ -2869,7 +2878,7 @@
     <row r="130" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="23">
         <f t="shared" si="5"/>
-        <v>3916000</v>
+        <v>4106000</v>
       </c>
       <c r="B130" s="23"/>
       <c r="C130" s="23"/>
@@ -2879,7 +2888,7 @@
     <row r="131" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="23">
         <f t="shared" si="5"/>
-        <v>3916000</v>
+        <v>4106000</v>
       </c>
       <c r="B131" s="23"/>
       <c r="C131" s="23"/>
@@ -2889,7 +2898,7 @@
     <row r="132" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="23">
         <f t="shared" si="5"/>
-        <v>3916000</v>
+        <v>4106000</v>
       </c>
       <c r="B132" s="23"/>
       <c r="C132" s="23"/>
@@ -2899,7 +2908,7 @@
     <row r="133" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="23">
         <f t="shared" si="5"/>
-        <v>3916000</v>
+        <v>4106000</v>
       </c>
       <c r="B133" s="23"/>
       <c r="C133" s="23"/>
@@ -2909,7 +2918,7 @@
     <row r="134" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="23">
         <f t="shared" si="5"/>
-        <v>3916000</v>
+        <v>4106000</v>
       </c>
       <c r="B134" s="23"/>
       <c r="C134" s="23"/>
@@ -2919,7 +2928,7 @@
     <row r="135" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="23">
         <f t="shared" si="5"/>
-        <v>3916000</v>
+        <v>4106000</v>
       </c>
       <c r="B135" s="23"/>
       <c r="C135" s="23"/>
@@ -2929,7 +2938,7 @@
     <row r="136" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="23">
         <f t="shared" si="5"/>
-        <v>3916000</v>
+        <v>4106000</v>
       </c>
       <c r="B136" s="23"/>
       <c r="C136" s="23"/>
@@ -2939,7 +2948,7 @@
     <row r="137" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="23">
         <f t="shared" si="5"/>
-        <v>3916000</v>
+        <v>4106000</v>
       </c>
       <c r="B137" s="23"/>
       <c r="C137" s="23"/>
@@ -2949,7 +2958,7 @@
     <row r="138" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="23">
         <f xml:space="preserve"> A137 +B138-C138</f>
-        <v>3916000</v>
+        <v>4106000</v>
       </c>
       <c r="B138" s="23"/>
       <c r="C138" s="23"/>
@@ -2960,7 +2969,7 @@
       <c r="A139" s="19"/>
       <c r="B139" s="17">
         <f>SUM(B119:B138)+B113</f>
-        <v>22791000</v>
+        <v>22981000</v>
       </c>
       <c r="C139" s="17">
         <f>SUM(C119:C138)+C113</f>
@@ -2981,7 +2990,7 @@
       <c r="B141" s="19"/>
       <c r="C141" s="25">
         <f>A138</f>
-        <v>3916000</v>
+        <v>4106000</v>
       </c>
       <c r="D141" s="26" t="s">
         <v>61</v>
